--- a/results/final_20260514_v2_summary/VirusPseAAC_ScoreVector_summary.xlsx
+++ b/results/final_20260514_v2_summary/VirusPseAAC_ScoreVector_summary.xlsx
@@ -2440,22 +2440,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.7905±0.0509</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7795±0.0448</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.7288±0.0624</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.6775±0.0690</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.7045±0.0152</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.5975±0.0600</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.5150±0.0812</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.5095±0.0794</t>
+          <t>nan±nan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
